--- a/Experimental Data/AVT1/AVTresults.xlsx
+++ b/Experimental Data/AVT1/AVTresults.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hanvit Lee\Documents\Julia\YJSPSim\AVT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Julia\YJSPSim\AVT1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81C4D748-8CBF-407E-9E8B-2E3A8D8E2BC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83184C26-9274-4BCB-965C-977898EE5274}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Accelerometer Covariance</t>
   </si>
@@ -47,22 +36,22 @@
     <t>Barometer Variance</t>
   </si>
   <si>
-    <t>Barometer-Predicted</t>
-  </si>
-  <si>
-    <t>Altitude Variance</t>
-  </si>
-  <si>
     <t>GPS Velocity Covariance</t>
   </si>
   <si>
-    <t>GPS</t>
-  </si>
-  <si>
-    <t>Latitude Variance</t>
-  </si>
-  <si>
-    <t>Longitude Variance</t>
+    <t>Barometer-Predicted Altitude Variance</t>
+  </si>
+  <si>
+    <t>GPS Latitude Variance</t>
+  </si>
+  <si>
+    <t>GPS Longitude Variance</t>
+  </si>
+  <si>
+    <t>GPS Altitude Variance</t>
+  </si>
+  <si>
+    <t>Magnetometer Covariance</t>
   </si>
 </sst>
 </file>
@@ -75,7 +64,7 @@
     <numFmt numFmtId="166" formatCode="0.00000000E+00"/>
     <numFmt numFmtId="167" formatCode="0.000000000"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -83,19 +72,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="10">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -111,19 +100,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -135,12 +112,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
+        <fgColor rgb="FFFFCCFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -163,30 +140,82 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFFCCFF"/>
+      <color rgb="FFFF99FF"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -462,66 +491,59 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="6"/>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7" t="s">
-        <v>3</v>
-      </c>
-      <c r="I1" s="9" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="11"/>
+      <c r="C1" s="11"/>
+      <c r="D1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="I1" s="13" t="s">
+        <v>5</v>
+      </c>
+      <c r="J1" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="9" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="9" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="10" t="s">
+      <c r="K1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="K2" s="10" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="12"/>
+      <c r="B2" s="12"/>
+      <c r="C2" s="12"/>
+      <c r="D2" s="8"/>
+      <c r="E2" s="8"/>
+      <c r="F2" s="8"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2.0423166413252899E-3</v>
       </c>
@@ -556,7 +578,7 @@
         <v>170.20130059811399</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3.1183385513645498E-5</v>
       </c>
@@ -576,7 +598,7 @@
         <v>-6.5158078548508596E-14</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>-1.9270988770272299E-4</v>
       </c>
@@ -596,19 +618,27 @@
         <v>2.7180339353827401E-12</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A6" s="9"/>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="9" t="s">
+        <v>3</v>
+      </c>
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A7" s="10" t="s">
-        <v>5</v>
-      </c>
+      <c r="D6" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="15"/>
+      <c r="F6" s="15"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="10"/>
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>5.1703284970418997E-2</v>
       </c>
@@ -618,8 +648,17 @@
       <c r="C8" s="3">
         <v>-4.74756133157039E-4</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D8" s="4">
+        <v>2.52548475572742E-5</v>
+      </c>
+      <c r="E8" s="4">
+        <v>-2.2690113742372702E-6</v>
+      </c>
+      <c r="F8" s="4">
+        <v>1.9717089589701401E-6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>-2.6569790187499199E-3</v>
       </c>
@@ -629,8 +668,17 @@
       <c r="C9" s="3">
         <v>1.53516147873292E-3</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="D9" s="4">
+        <v>-2.2690113742372702E-6</v>
+      </c>
+      <c r="E9" s="4">
+        <v>7.3530033662157798E-4</v>
+      </c>
+      <c r="F9" s="4">
+        <v>6.8719944229554404E-6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>-4.74756133157039E-4</v>
       </c>
@@ -640,8 +688,28 @@
       <c r="C10" s="3">
         <v>1.7364216422307299E-2</v>
       </c>
+      <c r="D10" s="4">
+        <v>1.9717089589701401E-6</v>
+      </c>
+      <c r="E10" s="4">
+        <v>6.8719944229554404E-6</v>
+      </c>
+      <c r="F10" s="4">
+        <v>3.9594665843786798E-5</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="J1:J2"/>
+    <mergeCell ref="K1:K2"/>
+    <mergeCell ref="D6:F7"/>
+    <mergeCell ref="A6:C7"/>
+    <mergeCell ref="A1:C2"/>
+    <mergeCell ref="D1:F2"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>